--- a/data/FRS_cleaned/Dec/Fmn D Dec/WorkOrderRemote_Dec 2025 D.xlsx
+++ b/data/FRS_cleaned/Dec/Fmn D Dec/WorkOrderRemote_Dec 2025 D.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\fwDemo\data\FRS_cleaned\Dec\Fmn D Dec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anu\APT\apt\army\fortwilliam\code\fwDemo\data\FRS_cleaned\Dec\Fmn D Dec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF65B831-5F39-4B98-996B-BBC3ED097F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C85DC4A-0C04-439F-8AD4-F1A6504D538F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="-15780" windowWidth="28800" windowHeight="15195" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Eng" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="173">
   <si>
     <r>
       <rPr>
@@ -4819,10 +4819,89 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
+    <t>Veh BA No</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>89X 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>111M</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">89X </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>583</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>P</t>
+    </r>
+  </si>
+  <si>
+    <t>Universal Joint</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Under collection</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030303"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -4831,645 +4910,476 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>on</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color rgb="FF030303"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>tro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363634"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">l </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>date</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>HI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>l</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">rt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ase </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>isposa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">l </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mech</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">lower </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>a</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tego</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ry  </t>
-    </r>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">d </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ar </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sel Cons</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>t o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">f 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tems</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>424Q.000107</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>28-0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ct-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>24</t>
+    </r>
+  </si>
+  <si>
+    <t>28-0ct-24</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Formation</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Make and Type)</t>
-    </r>
-  </si>
-  <si>
-    <t>Veh BA No</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>U8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>89X 6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>111M</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">89X </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>583</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>P</t>
-    </r>
-  </si>
-  <si>
-    <t>Universal Joint</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>Under collection</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>on</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tro</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363634"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">l </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>date</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>HI</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>l</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>I</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>e</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">rt </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ase </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>isposa</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">l </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Mech</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ro</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>or</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>b</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">lower </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">d </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ge</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ar </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>sel Cons</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>t o</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">f 5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tems</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>424Q.000107</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>28-0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ct-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>24</t>
-    </r>
-  </si>
-  <si>
-    <t>28-0ct-24</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>Formation</t>
-  </si>
-  <si>
-    <t>A6</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>A7</t>
-  </si>
-  <si>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>S</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>S</t>
+        <color rgb="FF757774"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF757774"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
         <color rgb="FF1C1D1C"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t>No</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tego</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ry  (Make and Type)</t>
     </r>
   </si>
   <si>
@@ -6572,6 +6482,9 @@
       </rPr>
       <t>SSNOR/Al/098</t>
     </r>
+  </si>
+  <si>
+    <t>Category</t>
   </si>
 </sst>
 </file>
@@ -6579,8 +6492,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="167" formatCode="[$-14009]dd/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="[$-14009]dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -6872,7 +6785,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -6909,7 +6822,7 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7125,56 +7038,59 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7482,35 +7398,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15BF3CFF-B171-44D9-B5BE-3C4491948958}">
   <dimension ref="A1:O6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.33203125" customWidth="1"/>
-    <col min="8" max="8" width="50.5" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.1640625" style="88" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="50.44140625" customWidth="1"/>
+    <col min="10" max="10" width="22.77734375" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" style="88" customWidth="1"/>
+    <col min="12" max="12" width="14.77734375" customWidth="1"/>
     <col min="13" max="13" width="14.33203125" style="88" customWidth="1"/>
     <col min="15" max="15" width="46.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="24" t="s">
-        <v>107</v>
-      </c>
       <c r="D1" s="25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E1" s="67" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F1" s="17" t="s">
         <v>1</v>
@@ -7534,33 +7450,33 @@
         <v>7</v>
       </c>
       <c r="M1" s="84" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N1" s="22" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
         <v>1</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C2" s="21" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -7590,7 +7506,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15">
         <v>2</v>
       </c>
@@ -7601,13 +7517,13 @@
         <v>18</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>19</v>
@@ -7637,7 +7553,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15">
         <v>3</v>
       </c>
@@ -7648,13 +7564,13 @@
         <v>26</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G4" s="69" t="s">
         <v>27</v>
@@ -7684,24 +7600,24 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="74">
         <v>4</v>
       </c>
       <c r="B5" s="75" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C5" s="76" t="s">
         <v>31</v>
       </c>
       <c r="D5" s="77" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="77" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F5" s="78" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G5" s="27" t="s">
         <v>32</v>
@@ -7731,27 +7647,27 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="63" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" s="63" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="74">
         <v>5</v>
       </c>
       <c r="B6" s="83" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" s="76" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D6" s="83" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E6" s="83" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F6" s="83" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>33</v>
@@ -7760,7 +7676,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="76" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K6" s="87">
         <v>45963</v>
@@ -7779,44 +7695,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B2C714C-5842-4352-8784-DCBCFC842B13}">
   <dimension ref="A1:O17"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="58"/>
     <col min="2" max="2" width="14" style="58" customWidth="1"/>
-    <col min="3" max="3" width="19.5" style="58" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" style="58" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="58" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" style="58" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" style="58" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" style="58" customWidth="1"/>
     <col min="7" max="7" width="32.6640625" style="58" customWidth="1"/>
-    <col min="8" max="8" width="44.5" style="58" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44.44140625" style="58" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.33203125" style="58"/>
     <col min="10" max="10" width="33.33203125" style="58" customWidth="1"/>
     <col min="11" max="11" width="14" style="97" customWidth="1"/>
     <col min="12" max="12" width="15.6640625" style="58" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" style="97" customWidth="1"/>
+    <col min="13" max="13" width="14.77734375" style="97" customWidth="1"/>
     <col min="14" max="14" width="9.33203125" style="58"/>
-    <col min="15" max="15" width="60.1640625" style="58" customWidth="1"/>
+    <col min="15" max="15" width="60.109375" style="58" customWidth="1"/>
     <col min="16" max="16384" width="9.33203125" style="58"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="56" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="56" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="45" t="s">
         <v>136</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="E1" s="68" t="s">
-        <v>153</v>
-      </c>
-      <c r="F1" s="45" t="s">
-        <v>138</v>
       </c>
       <c r="G1" s="45" t="s">
         <v>2</v>
@@ -7825,51 +7741,51 @@
         <v>3</v>
       </c>
       <c r="I1" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="J1" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="K1" s="93" t="s">
         <v>139</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="L1" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="K1" s="93" t="s">
+      <c r="M1" s="93" t="s">
         <v>141</v>
-      </c>
-      <c r="L1" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="M1" s="93" t="s">
-        <v>143</v>
       </c>
       <c r="N1" s="45" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>1</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>51</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F2" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G2" s="27" t="s">
         <v>52</v>
       </c>
       <c r="H2" s="37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I2" s="32">
         <v>1</v>
@@ -7887,30 +7803,30 @@
         <v>45814</v>
       </c>
       <c r="N2" s="35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O2" s="57" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
         <v>2</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C3" s="27" t="s">
         <v>62</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G3" s="27" t="s">
         <v>63</v>
@@ -7934,11 +7850,11 @@
         <v>45453</v>
       </c>
       <c r="N3" s="35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O3" s="57"/>
     </row>
-    <row r="4" spans="1:15" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>3</v>
       </c>
@@ -7949,16 +7865,16 @@
         <v>67</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H4" s="27" t="s">
         <v>68</v>
@@ -7967,10 +7883,10 @@
         <v>1</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K4" s="94" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L4" s="31">
         <v>243001650</v>
@@ -7979,13 +7895,13 @@
         <v>45609</v>
       </c>
       <c r="N4" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O4" s="57" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="30">
         <v>4</v>
       </c>
@@ -7993,16 +7909,16 @@
         <v>69</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G5" s="27" t="s">
         <v>70</v>
@@ -8017,7 +7933,7 @@
         <v>72</v>
       </c>
       <c r="K5" s="95" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L5" s="31">
         <v>241010808</v>
@@ -8026,30 +7942,30 @@
         <v>45609</v>
       </c>
       <c r="N5" s="35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O5" s="57" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="32">
         <v>5</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="27" t="s">
         <v>58</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G6" s="27" t="s">
         <v>59</v>
@@ -8073,11 +7989,11 @@
         <v>45453</v>
       </c>
       <c r="N6" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O6" s="57"/>
     </row>
-    <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="30">
         <v>6</v>
       </c>
@@ -8088,19 +8004,19 @@
         <v>73</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I7" s="29">
         <v>1</v>
@@ -8118,28 +8034,28 @@
         <v>75</v>
       </c>
       <c r="N7" s="35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O7" s="57"/>
     </row>
-    <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="32">
         <v>7</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C8" s="27" t="s">
         <v>76</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G8" s="27" t="s">
         <v>77</v>
@@ -8163,31 +8079,31 @@
         <v>75</v>
       </c>
       <c r="N8" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O8" s="57"/>
     </row>
-    <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="30">
         <v>8</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C9" s="27" t="s">
         <v>81</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H9" s="27" t="s">
         <v>82</v>
@@ -8208,28 +8124,28 @@
         <v>45717</v>
       </c>
       <c r="N9" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O9" s="57"/>
     </row>
-    <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="32">
         <v>9</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C10" s="27" t="s">
         <v>84</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G10" s="27" t="s">
         <v>85</v>
@@ -8253,33 +8169,33 @@
         <v>45717</v>
       </c>
       <c r="N10" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O10" s="57" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="30">
         <v>10</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>88</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H11" s="27" t="s">
         <v>89</v>
@@ -8300,28 +8216,28 @@
         <v>45719</v>
       </c>
       <c r="N11" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O11" s="57"/>
     </row>
-    <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="32">
         <v>11</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>91</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G12" s="27" t="s">
         <v>92</v>
@@ -8345,28 +8261,28 @@
         <v>45735</v>
       </c>
       <c r="N12" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O12" s="57"/>
     </row>
-    <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="30">
         <v>12</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G13" s="27" t="s">
         <v>95</v>
@@ -8390,28 +8306,28 @@
         <v>75</v>
       </c>
       <c r="N13" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O13" s="57"/>
     </row>
-    <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="32">
         <v>13</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C14" s="27" t="s">
         <v>54</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G14" s="27" t="s">
         <v>55</v>
@@ -8435,28 +8351,28 @@
         <v>45453</v>
       </c>
       <c r="N14" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O14" s="57"/>
     </row>
-    <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>14</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>99</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G15" s="27" t="s">
         <v>100</v>
@@ -8480,28 +8396,28 @@
         <v>45874</v>
       </c>
       <c r="N15" s="35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O15" s="57"/>
     </row>
-    <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32">
         <v>15</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G16" s="27" t="s">
         <v>103</v>
@@ -8525,11 +8441,11 @@
         <v>98</v>
       </c>
       <c r="N16" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O16" s="57"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="57"/>
       <c r="B17" s="57"/>
       <c r="C17" s="57"/>
@@ -8555,15 +8471,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC9CB67-069E-4DDA-927B-C96C93506AB7}">
   <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" style="63" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.77734375" style="63" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" style="63" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.1640625" style="63" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="63" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="63" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" style="63" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="63" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" style="63" customWidth="1"/>
-    <col min="7" max="7" width="25.5" style="63" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.44140625" style="63" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.6640625" style="63" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="4.6640625" style="63" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22" style="63" bestFit="1" customWidth="1"/>
@@ -8575,24 +8491,24 @@
     <col min="16" max="16384" width="9.33203125" style="63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="59" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="59" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="101" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="45" t="s">
         <v>136</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="E1" s="68" t="s">
-        <v>153</v>
-      </c>
-      <c r="F1" s="45" t="s">
-        <v>138</v>
       </c>
       <c r="G1" s="45" t="s">
         <v>2</v>
@@ -8601,51 +8517,51 @@
         <v>3</v>
       </c>
       <c r="I1" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="J1" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="K1" s="93" t="s">
         <v>139</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="L1" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="K1" s="93" t="s">
+      <c r="M1" s="93" t="s">
         <v>141</v>
-      </c>
-      <c r="L1" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="M1" s="93" t="s">
-        <v>143</v>
       </c>
       <c r="N1" s="45" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="60">
         <v>1</v>
       </c>
       <c r="B2" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F2" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>110</v>
-      </c>
       <c r="G2" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I2" s="39">
         <v>1</v>
@@ -8663,35 +8579,35 @@
         <v>45405</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O2" s="61"/>
       <c r="P2" s="62"/>
     </row>
-    <row r="3" spans="1:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="64">
         <v>2</v>
       </c>
       <c r="B3" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F3" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>110</v>
-      </c>
       <c r="G3" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I3" s="39">
         <v>1</v>
@@ -8714,36 +8630,36 @@
       <c r="O3" s="61"/>
       <c r="P3" s="62"/>
     </row>
-    <row r="4" spans="1:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="64">
         <v>2</v>
       </c>
       <c r="B4" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F4" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="D4" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>158</v>
-      </c>
       <c r="H4" s="26" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I4" s="39">
         <v>1</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K4" s="100">
         <v>45752</v>
@@ -8756,36 +8672,36 @@
       <c r="O4" s="61"/>
       <c r="P4" s="62"/>
     </row>
-    <row r="5" spans="1:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="64">
         <v>2</v>
       </c>
       <c r="B5" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F5" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="D5" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="F5" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>159</v>
-      </c>
       <c r="H5" s="26" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I5" s="39">
         <v>1</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K5" s="100">
         <v>45295</v>
@@ -8802,7 +8718,7 @@
       <c r="O5" s="61"/>
       <c r="P5" s="62"/>
     </row>
-    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="49">
         <v>3</v>
       </c>
@@ -8810,19 +8726,19 @@
         <v>40</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F6" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>41</v>
@@ -8843,12 +8759,12 @@
         <v>45921</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O6" s="61"/>
       <c r="P6" s="62"/>
     </row>
-    <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="50">
         <v>4</v>
       </c>
@@ -8859,13 +8775,13 @@
         <v>47</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F7" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G7" s="12">
         <v>2920.0019080000002</v>
@@ -8889,35 +8805,35 @@
         <v>50</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O7" s="65"/>
       <c r="P7" s="66"/>
     </row>
-    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="52">
         <v>5</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>44</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I8" s="41">
         <v>1</v>
@@ -8935,12 +8851,12 @@
         <v>45404</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O8" s="65"/>
       <c r="P8" s="66"/>
     </row>
-    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="32"/>
       <c r="B9" s="27"/>
       <c r="C9" s="27"/>
@@ -8957,7 +8873,7 @@
       <c r="N9" s="35"/>
       <c r="O9" s="57"/>
     </row>
-    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="30"/>
       <c r="B10" s="28"/>
       <c r="C10" s="27"/>
@@ -8974,7 +8890,7 @@
       <c r="N10" s="35"/>
       <c r="O10" s="57"/>
     </row>
-    <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="29"/>
       <c r="B11" s="28"/>
       <c r="C11" s="27"/>
@@ -8991,7 +8907,7 @@
       <c r="N11" s="35"/>
       <c r="O11" s="57"/>
     </row>
-    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="30"/>
       <c r="B12" s="28"/>
       <c r="C12" s="27"/>
@@ -9008,7 +8924,7 @@
       <c r="N12" s="35"/>
       <c r="O12" s="57"/>
     </row>
-    <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="30"/>
       <c r="B13" s="27"/>
       <c r="C13" s="27"/>
@@ -9025,7 +8941,7 @@
       <c r="N13" s="35"/>
       <c r="O13" s="57"/>
     </row>
-    <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
       <c r="C14" s="33"/>
@@ -9042,7 +8958,7 @@
       <c r="N14" s="35"/>
       <c r="O14" s="57"/>
     </row>
-    <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="29"/>
       <c r="B15" s="27"/>
       <c r="C15" s="28"/>
@@ -9059,7 +8975,7 @@
       <c r="N15" s="35"/>
       <c r="O15" s="57"/>
     </row>
-    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32"/>
       <c r="B16" s="28"/>
       <c r="C16" s="27"/>
@@ -9076,7 +8992,7 @@
       <c r="N16" s="35"/>
       <c r="O16" s="57"/>
     </row>
-    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="29"/>
       <c r="B17" s="27"/>
       <c r="C17" s="27"/>
@@ -9093,7 +9009,7 @@
       <c r="N17" s="35"/>
       <c r="O17" s="57"/>
     </row>
-    <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="30"/>
       <c r="B18" s="28"/>
       <c r="C18" s="27"/>
@@ -9110,7 +9026,7 @@
       <c r="N18" s="35"/>
       <c r="O18" s="57"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="57"/>
       <c r="B19" s="57"/>
       <c r="C19" s="57"/>

--- a/data/FRS_cleaned/Dec/Fmn D Dec/WorkOrderRemote_Dec 2025 D.xlsx
+++ b/data/FRS_cleaned/Dec/Fmn D Dec/WorkOrderRemote_Dec 2025 D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\fwDemo\data\FRS_cleaned\Dec\Fmn D Dec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF65B831-5F39-4B98-996B-BBC3ED097F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD92A6B-205A-4DB1-8EF5-DAD6D8F2AC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="-8130" windowWidth="28755" windowHeight="7800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Eng" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="181">
   <si>
     <r>
       <rPr>
@@ -3687,8 +3687,140 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>01X 8565</t>
-    </r>
+      <t xml:space="preserve">NBC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>FIit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">r </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>FA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">T </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SS/EONAS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>016</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0X 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>102S4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>X</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3698,25 +3830,229 @@
       </rPr>
       <t>A</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">NBC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>FIit</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>·1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>KV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>r Co</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>pres</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Wi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>h Deflecto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>r</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SS/EONAAT/018</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>06X 9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>19M</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">re </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
     </r>
     <r>
       <rPr>
@@ -3734,41 +4070,23 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">r </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>FA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">T </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -3777,32 +4095,133 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>SS/EONAS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
         <color rgb="FF363836"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>016</t>
-    </r>
-  </si>
-  <si>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>S/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>19</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>584M</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">AK </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3819,92 +4238,65 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>0X 0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>102S4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>X</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>50</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>KV</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A</t>
+      <t>50 MKV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Air Co</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>pressor With Deflecto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>r</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SS/EONAAT</t>
     </r>
     <r>
       <rPr>
@@ -3913,6 +4305,956 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>/0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>599</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>5-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>522</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Wirin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>g Ha</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mess B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">anced </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cable No-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4D4F4D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(St</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SS/EONT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>72/01</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NYR</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8X 57</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>14H</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>995-002</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>22</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Wiri</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>rness B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nced(Cable No-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>t,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TSS/EONT-72/02</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">N1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/R72 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1S.00289</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>7 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Recupe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tor</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SS/EONT-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2105</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030303"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tego</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030303"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ry  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF030303"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Make and Type)</t>
+    </r>
+  </si>
+  <si>
+    <t>Veh BA No</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>89X 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>111M</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">89X </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>583</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>P</t>
+    </r>
+  </si>
+  <si>
+    <t>Universal Joint</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Under collection</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030303"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>on</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030303"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363634"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">l </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>date</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>HI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>l</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">rt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ase </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>isposa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">l </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mech</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">lower </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">d </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ar </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sel Cons</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>i</t>
     </r>
     <r>
@@ -3922,25 +5264,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>r Co</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>pres</t>
+      <t>s</t>
     </r>
     <r>
       <rPr>
@@ -3949,16 +5273,67 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">or </t>
+      <t>t o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">f 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tems</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>424Q.000107</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>28-0</t>
     </r>
     <r>
       <rPr>
@@ -3967,1401 +5342,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Wi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>h Deflecto</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>r</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>SS/EONAAT/018</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>06X 9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>19M</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">re </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>e</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ter</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>S/E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>O</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>19</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>8X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>584M</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">AK </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>50 MKV</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Air Co</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>pressor With Deflecto</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>r</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>SS/EONAAT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>20</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>599</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>5-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>522</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Wirin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>g Ha</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>mess B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>r</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">anced </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Cable No-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF4D4F4D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(St</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>SS/EONT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>72/01</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>NYR</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>8X 57</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>14H</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>995-002</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>22</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Wiri</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>rness B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ra</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>nced(Cable No-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>t,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>TSS/EONT-72/02</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">N1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/R72 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1S.00289</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>7 1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Recupe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ra</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tor</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>SS/EONT-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2105</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tego</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ry  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Make and Type)</t>
-    </r>
-  </si>
-  <si>
-    <t>Veh BA No</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>U8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>89X 6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>111M</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">89X </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>583</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>P</t>
-    </r>
-  </si>
-  <si>
-    <t>Universal Joint</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>Under collection</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>on</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tro</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363634"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">l </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>date</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>HI</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>l</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>I</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>e</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">rt </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ase </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>isposa</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">l </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Mech</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ro</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>or</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>b</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">lower </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">d </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ge</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ar </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>sel Cons</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>t o</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">f 5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tems</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>424Q.000107</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>28-0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>ct-</t>
     </r>
     <r>
@@ -5388,9 +5368,6 @@
   </si>
   <si>
     <t>A1</t>
-  </si>
-  <si>
-    <t>A3</t>
   </si>
   <si>
     <t>A4</t>
@@ -6571,6 +6548,162 @@
         <family val="2"/>
       </rPr>
       <t>SSNOR/Al/098</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>424Q.000107</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-9846</t>
+    </r>
+  </si>
+  <si>
+    <t>Headlight</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SS/EONAS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>09/2036</t>
+    </r>
+  </si>
+  <si>
+    <t>04X94W87</t>
+  </si>
+  <si>
+    <t>04X94W88</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030303"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>7X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030303"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>416YT56</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030303"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Bb </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363634"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>301-00-27RT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030303"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SSNOR/Al/076-AD</t>
     </r>
   </si>
 </sst>
@@ -6579,8 +6712,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="167" formatCode="[$-14009]dd/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="[$-14009]dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -6909,7 +7042,7 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7125,55 +7258,55 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7481,7 +7614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15BF3CFF-B171-44D9-B5BE-3C4491948958}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.5" customWidth="1"/>
@@ -7501,16 +7634,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="24" t="s">
-        <v>107</v>
-      </c>
       <c r="D1" s="25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E1" s="67" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F1" s="17" t="s">
         <v>1</v>
@@ -7534,13 +7667,13 @@
         <v>7</v>
       </c>
       <c r="M1" s="84" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N1" s="22" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7548,19 +7681,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C2" s="21" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -7601,13 +7734,13 @@
         <v>18</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>19</v>
@@ -7648,13 +7781,13 @@
         <v>26</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G4" s="69" t="s">
         <v>27</v>
@@ -7689,19 +7822,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="75" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C5" s="76" t="s">
         <v>31</v>
       </c>
       <c r="D5" s="77" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="77" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F5" s="78" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G5" s="27" t="s">
         <v>32</v>
@@ -7736,22 +7869,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="83" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" s="76" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D6" s="83" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E6" s="83" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F6" s="83" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>33</v>
@@ -7760,7 +7893,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="76" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K6" s="87">
         <v>45963</v>
@@ -7769,6 +7902,51 @@
       <c r="M6" s="87"/>
       <c r="N6" s="83"/>
       <c r="O6" s="83"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="74">
+        <v>6</v>
+      </c>
+      <c r="B7" s="83" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="76" t="s">
+        <v>178</v>
+      </c>
+      <c r="D7" s="83" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="83" t="s">
+        <v>152</v>
+      </c>
+      <c r="F7" s="83" t="s">
+        <v>109</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="83">
+        <v>1</v>
+      </c>
+      <c r="J7" s="76" t="s">
+        <v>180</v>
+      </c>
+      <c r="K7" s="87">
+        <v>45986</v>
+      </c>
+      <c r="L7" s="83">
+        <v>7643097</v>
+      </c>
+      <c r="M7" s="87">
+        <v>45989</v>
+      </c>
+      <c r="N7" s="83" t="s">
+        <v>113</v>
+      </c>
+      <c r="O7" s="83"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7778,7 +7956,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B2C714C-5842-4352-8784-DCBCFC842B13}">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="58"/>
@@ -7801,22 +7979,22 @@
   <sheetData>
     <row r="1" spans="1:15" s="56" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="45" t="s">
         <v>136</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="E1" s="68" t="s">
-        <v>153</v>
-      </c>
-      <c r="F1" s="45" t="s">
-        <v>138</v>
       </c>
       <c r="G1" s="45" t="s">
         <v>2</v>
@@ -7825,25 +8003,25 @@
         <v>3</v>
       </c>
       <c r="I1" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="J1" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="K1" s="93" t="s">
         <v>139</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="L1" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="K1" s="93" t="s">
+      <c r="M1" s="93" t="s">
         <v>141</v>
-      </c>
-      <c r="L1" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="M1" s="93" t="s">
-        <v>143</v>
       </c>
       <c r="N1" s="45" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -7851,25 +8029,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>51</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F2" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G2" s="27" t="s">
         <v>52</v>
       </c>
       <c r="H2" s="37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I2" s="32">
         <v>1</v>
@@ -7887,30 +8065,30 @@
         <v>45814</v>
       </c>
       <c r="N2" s="35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O2" s="57" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="30">
+      <c r="A3" s="32">
         <v>2</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C3" s="27" t="s">
         <v>62</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G3" s="27" t="s">
         <v>63</v>
@@ -7934,7 +8112,7 @@
         <v>45453</v>
       </c>
       <c r="N3" s="35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O3" s="57"/>
     </row>
@@ -7949,16 +8127,16 @@
         <v>67</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H4" s="27" t="s">
         <v>68</v>
@@ -7967,10 +8145,10 @@
         <v>1</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K4" s="94" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L4" s="31">
         <v>243001650</v>
@@ -7979,30 +8157,30 @@
         <v>45609</v>
       </c>
       <c r="N4" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O4" s="57" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30">
+      <c r="A5" s="32">
         <v>4</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>69</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G5" s="27" t="s">
         <v>70</v>
@@ -8017,7 +8195,7 @@
         <v>72</v>
       </c>
       <c r="K5" s="95" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L5" s="31">
         <v>241010808</v>
@@ -8026,10 +8204,10 @@
         <v>45609</v>
       </c>
       <c r="N5" s="35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O5" s="57" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -8037,19 +8215,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="27" t="s">
         <v>58</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G6" s="27" t="s">
         <v>59</v>
@@ -8073,12 +8251,12 @@
         <v>45453</v>
       </c>
       <c r="N6" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O6" s="57"/>
     </row>
     <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="30">
+      <c r="A7" s="32">
         <v>6</v>
       </c>
       <c r="B7" s="27" t="s">
@@ -8088,19 +8266,19 @@
         <v>73</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I7" s="29">
         <v>1</v>
@@ -8118,7 +8296,7 @@
         <v>75</v>
       </c>
       <c r="N7" s="35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O7" s="57"/>
     </row>
@@ -8127,19 +8305,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C8" s="27" t="s">
         <v>76</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G8" s="27" t="s">
         <v>77</v>
@@ -8154,7 +8332,7 @@
         <v>79</v>
       </c>
       <c r="K8" s="94">
-        <v>45677</v>
+        <v>45981</v>
       </c>
       <c r="L8" s="35" t="s">
         <v>80</v>
@@ -8163,40 +8341,40 @@
         <v>75</v>
       </c>
       <c r="N8" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O8" s="57"/>
     </row>
     <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="30">
+      <c r="A9" s="32">
         <v>8</v>
       </c>
       <c r="B9" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="27" t="s">
         <v>81</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="H9" s="27" t="s">
-        <v>82</v>
       </c>
       <c r="I9" s="30">
         <v>1</v>
       </c>
       <c r="J9" s="35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K9" s="94">
         <v>45702</v>
@@ -8208,7 +8386,7 @@
         <v>45717</v>
       </c>
       <c r="N9" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O9" s="57"/>
     </row>
@@ -8217,180 +8395,174 @@
         <v>9</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>84</v>
+        <v>133</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>176</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>166</v>
+        <v>128</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>152</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>85</v>
+        <v>172</v>
       </c>
       <c r="H10" s="27" t="s">
-        <v>86</v>
+        <v>173</v>
       </c>
       <c r="I10" s="30">
         <v>1</v>
       </c>
       <c r="J10" s="35" t="s">
-        <v>87</v>
+        <v>174</v>
       </c>
       <c r="K10" s="94">
-        <v>45702</v>
-      </c>
-      <c r="L10" s="36">
-        <v>241015396</v>
-      </c>
-      <c r="M10" s="94">
-        <v>45717</v>
-      </c>
-      <c r="N10" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="O10" s="57" t="s">
-        <v>152</v>
-      </c>
+        <v>45964</v>
+      </c>
+      <c r="L10" s="36"/>
+      <c r="M10" s="94"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="57"/>
     </row>
     <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="30">
+      <c r="A11" s="32">
         <v>10</v>
       </c>
-      <c r="B11" s="27" t="s">
-        <v>126</v>
+      <c r="B11" s="28" t="s">
+        <v>132</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>162</v>
+        <v>128</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>164</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I11" s="30">
         <v>1</v>
       </c>
       <c r="J11" s="35" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K11" s="94">
-        <v>45709</v>
+        <v>45702</v>
       </c>
       <c r="L11" s="36">
-        <v>241015532</v>
+        <v>241015396</v>
       </c>
       <c r="M11" s="94">
-        <v>45719</v>
+        <v>45717</v>
       </c>
       <c r="N11" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="O11" s="57"/>
+        <v>120</v>
+      </c>
+      <c r="O11" s="57" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="32">
         <v>11</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="I12" s="32">
+        <v>88</v>
+      </c>
+      <c r="I12" s="30">
         <v>1</v>
       </c>
       <c r="J12" s="35" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K12" s="94">
-        <v>45720</v>
+        <v>45709</v>
       </c>
       <c r="L12" s="36">
-        <v>241016229</v>
+        <v>241015532</v>
       </c>
       <c r="M12" s="94">
-        <v>45735</v>
+        <v>45719</v>
       </c>
       <c r="N12" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O12" s="57"/>
     </row>
     <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="30">
+      <c r="A13" s="32">
         <v>12</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>151</v>
+        <v>125</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>90</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>166</v>
+        <v>128</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>163</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="I13" s="30">
+        <v>92</v>
+      </c>
+      <c r="I13" s="32">
         <v>1</v>
       </c>
       <c r="J13" s="35" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="K13" s="94">
-        <v>45825</v>
-      </c>
-      <c r="L13" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="M13" s="94" t="s">
-        <v>75</v>
+        <v>45720</v>
+      </c>
+      <c r="L13" s="36">
+        <v>241016229</v>
+      </c>
+      <c r="M13" s="94">
+        <v>45735</v>
       </c>
       <c r="N13" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O13" s="57"/>
     </row>
@@ -8398,89 +8570,89 @@
       <c r="A14" s="32">
         <v>13</v>
       </c>
-      <c r="B14" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>54</v>
+      <c r="B14" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>149</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="34" t="s">
         <v>164</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="H14" s="27" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="I14" s="30">
         <v>1</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="K14" s="94">
-        <v>45432</v>
-      </c>
-      <c r="L14" s="31">
-        <v>241001943</v>
-      </c>
-      <c r="M14" s="94">
-        <v>45453</v>
+        <v>45825</v>
+      </c>
+      <c r="L14" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="M14" s="94" t="s">
+        <v>75</v>
       </c>
       <c r="N14" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O14" s="57"/>
     </row>
     <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="30">
+      <c r="A15" s="32">
         <v>14</v>
       </c>
-      <c r="B15" s="27" t="s">
-        <v>135</v>
+      <c r="B15" s="28" t="s">
+        <v>133</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="I15" s="29">
+        <v>56</v>
+      </c>
+      <c r="I15" s="30">
         <v>1</v>
       </c>
       <c r="J15" s="35" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="K15" s="94">
-        <v>45675</v>
-      </c>
-      <c r="L15" s="36">
-        <v>251009621</v>
+        <v>45432</v>
+      </c>
+      <c r="L15" s="31">
+        <v>241001943</v>
       </c>
       <c r="M15" s="94">
-        <v>45874</v>
+        <v>45453</v>
       </c>
       <c r="N15" s="35" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="O15" s="57"/>
     </row>
@@ -8488,63 +8660,108 @@
       <c r="A16" s="32">
         <v>15</v>
       </c>
-      <c r="B16" s="28" t="s">
-        <v>135</v>
+      <c r="B16" s="27" t="s">
+        <v>133</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>167</v>
+        <v>98</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H16" s="27" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I16" s="29">
         <v>1</v>
       </c>
       <c r="J16" s="35" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="K16" s="94">
-        <v>45897</v>
-      </c>
-      <c r="L16" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="M16" s="94" t="s">
-        <v>98</v>
+        <v>45675</v>
+      </c>
+      <c r="L16" s="36">
+        <v>251009621</v>
+      </c>
+      <c r="M16" s="94">
+        <v>45874</v>
       </c>
       <c r="N16" s="35" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="O16" s="57"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A17" s="57"/>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="96"/>
-      <c r="L17" s="57"/>
-      <c r="M17" s="96"/>
-      <c r="N17" s="57"/>
+    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="32">
+        <v>16</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="I17" s="29">
+        <v>1</v>
+      </c>
+      <c r="J17" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="K17" s="94">
+        <v>45897</v>
+      </c>
+      <c r="L17" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="94" t="s">
+        <v>97</v>
+      </c>
+      <c r="N17" s="35" t="s">
+        <v>120</v>
+      </c>
       <c r="O17" s="57"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18" s="57"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="57"/>
+      <c r="M18" s="96"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="57"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
@@ -8577,22 +8794,22 @@
   <sheetData>
     <row r="1" spans="1:16" s="59" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="45" t="s">
         <v>136</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>137</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="E1" s="68" t="s">
-        <v>153</v>
-      </c>
-      <c r="F1" s="45" t="s">
-        <v>138</v>
       </c>
       <c r="G1" s="45" t="s">
         <v>2</v>
@@ -8601,25 +8818,25 @@
         <v>3</v>
       </c>
       <c r="I1" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="J1" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="K1" s="93" t="s">
         <v>139</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="L1" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="K1" s="93" t="s">
+      <c r="M1" s="93" t="s">
         <v>141</v>
-      </c>
-      <c r="L1" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="M1" s="93" t="s">
-        <v>143</v>
       </c>
       <c r="N1" s="45" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -8627,25 +8844,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F2" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>110</v>
-      </c>
       <c r="G2" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I2" s="39">
         <v>1</v>
@@ -8663,7 +8880,7 @@
         <v>45405</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O2" s="61"/>
       <c r="P2" s="62"/>
@@ -8673,25 +8890,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F3" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>110</v>
-      </c>
       <c r="G3" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I3" s="39">
         <v>1</v>
@@ -8719,31 +8936,31 @@
         <v>2</v>
       </c>
       <c r="B4" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F4" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="D4" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>158</v>
-      </c>
       <c r="H4" s="26" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I4" s="39">
         <v>1</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K4" s="100">
         <v>45752</v>
@@ -8761,31 +8978,31 @@
         <v>2</v>
       </c>
       <c r="B5" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F5" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="D5" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="F5" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>159</v>
-      </c>
       <c r="H5" s="26" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I5" s="39">
         <v>1</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K5" s="100">
         <v>45295</v>
@@ -8810,19 +9027,19 @@
         <v>40</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F6" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>41</v>
@@ -8843,7 +9060,7 @@
         <v>45921</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O6" s="61"/>
       <c r="P6" s="62"/>
@@ -8859,13 +9076,13 @@
         <v>47</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F7" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G7" s="12">
         <v>2920.0019080000002</v>
@@ -8889,7 +9106,7 @@
         <v>50</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O7" s="65"/>
       <c r="P7" s="66"/>
@@ -8899,25 +9116,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>44</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I8" s="41">
         <v>1</v>
@@ -8935,7 +9152,7 @@
         <v>45404</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O8" s="65"/>
       <c r="P8" s="66"/>

--- a/data/FRS_cleaned/Dec/Fmn D Dec/WorkOrderRemote_Dec 2025 D.xlsx
+++ b/data/FRS_cleaned/Dec/Fmn D Dec/WorkOrderRemote_Dec 2025 D.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\fwDemo\data\FRS_cleaned\Dec\Fmn D Dec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anu\APT\apt\army\fortwilliam\code\fwDemo\data\FRS_cleaned\Dec\Fmn D Dec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD92A6B-205A-4DB1-8EF5-DAD6D8F2AC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B176F10-2386-41E4-8C59-E63184700CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="-8130" windowWidth="28755" windowHeight="7800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Eng" sheetId="2" r:id="rId1"/>
@@ -4799,10 +4799,89 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
+    <t>Veh BA No</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>89X 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>111M</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">89X </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>583</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>P</t>
+    </r>
+  </si>
+  <si>
+    <t>Universal Joint</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Under collection</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030303"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -4811,642 +4890,473 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>on</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color rgb="FF030303"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>tro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363634"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">l </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>date</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>HI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>l</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">rt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ase </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>isposa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">l </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mech</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">lower </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>a</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tego</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ry  </t>
-    </r>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">d </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ar </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sel Cons</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>t o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">f 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tems</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>424Q.000107</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>28-0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ct-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>24</t>
+    </r>
+  </si>
+  <si>
+    <t>28-0ct-24</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Formation</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Make and Type)</t>
-    </r>
-  </si>
-  <si>
-    <t>Veh BA No</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>U8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>89X 6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>111M</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">89X </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>583</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>P</t>
-    </r>
-  </si>
-  <si>
-    <t>Universal Joint</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>Under collection</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>on</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tro</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363634"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">l </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>date</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>HI</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>l</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>I</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>e</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">rt </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ase </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>isposa</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">l </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Mech</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ro</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>or</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>b</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">lower </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">d </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ge</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ar </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>sel Cons</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>t o</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">f 5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tems</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>424Q.000107</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>28-0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ct-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>24</t>
-    </r>
-  </si>
-  <si>
-    <t>28-0ct-24</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>Formation</t>
-  </si>
-  <si>
-    <t>A6</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>A7</t>
-  </si>
-  <si>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>S</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>S</t>
+        <color rgb="FF757774"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF757774"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
         <color rgb="FF1C1D1C"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t>No</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tego</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ry  (Make and Type)</t>
     </r>
   </si>
   <si>
@@ -6705,6 +6615,12 @@
       </rPr>
       <t>SSNOR/Al/076-AD</t>
     </r>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Unit</t>
   </si>
 </sst>
 </file>
@@ -7615,35 +7531,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15BF3CFF-B171-44D9-B5BE-3C4491948958}">
   <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.33203125" customWidth="1"/>
-    <col min="8" max="8" width="50.5" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.1640625" style="88" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="50.44140625" customWidth="1"/>
+    <col min="10" max="10" width="22.77734375" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" style="88" customWidth="1"/>
+    <col min="12" max="12" width="14.77734375" customWidth="1"/>
     <col min="13" max="13" width="14.33203125" style="88" customWidth="1"/>
     <col min="15" max="15" width="46.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="24" t="s">
-        <v>106</v>
-      </c>
       <c r="D1" s="25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E1" s="67" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F1" s="17" t="s">
         <v>1</v>
@@ -7667,33 +7583,33 @@
         <v>7</v>
       </c>
       <c r="M1" s="84" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N1" s="22" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
         <v>1</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C2" s="21" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -7723,7 +7639,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15">
         <v>2</v>
       </c>
@@ -7734,13 +7650,13 @@
         <v>18</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>19</v>
@@ -7770,7 +7686,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15">
         <v>3</v>
       </c>
@@ -7781,13 +7697,13 @@
         <v>26</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G4" s="69" t="s">
         <v>27</v>
@@ -7817,24 +7733,24 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="74">
         <v>4</v>
       </c>
       <c r="B5" s="75" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C5" s="76" t="s">
         <v>31</v>
       </c>
       <c r="D5" s="77" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E5" s="77" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F5" s="78" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G5" s="27" t="s">
         <v>32</v>
@@ -7864,27 +7780,27 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="63" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" s="63" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="74">
         <v>5</v>
       </c>
       <c r="B6" s="83" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C6" s="76" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D6" s="83" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E6" s="83" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F6" s="83" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>33</v>
@@ -7893,7 +7809,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="76" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K6" s="87">
         <v>45963</v>
@@ -7903,27 +7819,27 @@
       <c r="N6" s="83"/>
       <c r="O6" s="83"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="74">
         <v>6</v>
       </c>
       <c r="B7" s="83" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="83" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" s="83" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" s="83" t="s">
+        <v>108</v>
+      </c>
+      <c r="G7" s="27" t="s">
         <v>177</v>
-      </c>
-      <c r="C7" s="76" t="s">
-        <v>178</v>
-      </c>
-      <c r="D7" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="E7" s="83" t="s">
-        <v>152</v>
-      </c>
-      <c r="F7" s="83" t="s">
-        <v>109</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>179</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>33</v>
@@ -7932,7 +7848,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="76" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K7" s="87">
         <v>45986</v>
@@ -7944,7 +7860,7 @@
         <v>45989</v>
       </c>
       <c r="N7" s="83" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O7" s="83"/>
     </row>
@@ -7957,44 +7873,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B2C714C-5842-4352-8784-DCBCFC842B13}">
   <dimension ref="A1:O18"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="58"/>
     <col min="2" max="2" width="14" style="58" customWidth="1"/>
-    <col min="3" max="3" width="19.5" style="58" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" style="58" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="58" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" style="58" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" style="58" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" style="58" customWidth="1"/>
     <col min="7" max="7" width="32.6640625" style="58" customWidth="1"/>
-    <col min="8" max="8" width="44.5" style="58" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44.44140625" style="58" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.33203125" style="58"/>
     <col min="10" max="10" width="33.33203125" style="58" customWidth="1"/>
     <col min="11" max="11" width="14" style="97" customWidth="1"/>
     <col min="12" max="12" width="15.6640625" style="58" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" style="97" customWidth="1"/>
+    <col min="13" max="13" width="14.77734375" style="97" customWidth="1"/>
     <col min="14" max="14" width="9.33203125" style="58"/>
-    <col min="15" max="15" width="60.1640625" style="58" customWidth="1"/>
+    <col min="15" max="15" width="60.109375" style="58" customWidth="1"/>
     <col min="16" max="16384" width="9.33203125" style="58"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="56" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="56" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1" s="45" t="s">
         <v>134</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="D1" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1" s="68" t="s">
-        <v>151</v>
-      </c>
-      <c r="F1" s="45" t="s">
-        <v>136</v>
       </c>
       <c r="G1" s="45" t="s">
         <v>2</v>
@@ -8003,51 +7919,51 @@
         <v>3</v>
       </c>
       <c r="I1" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="J1" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" s="93" t="s">
         <v>137</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="L1" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="K1" s="93" t="s">
+      <c r="M1" s="93" t="s">
         <v>139</v>
-      </c>
-      <c r="L1" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="M1" s="93" t="s">
-        <v>141</v>
       </c>
       <c r="N1" s="45" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="54" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>1</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>51</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F2" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G2" s="27" t="s">
         <v>52</v>
       </c>
       <c r="H2" s="37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I2" s="32">
         <v>1</v>
@@ -8065,30 +7981,30 @@
         <v>45814</v>
       </c>
       <c r="N2" s="35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O2" s="57" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="32">
         <v>2</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C3" s="27" t="s">
         <v>62</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G3" s="27" t="s">
         <v>63</v>
@@ -8112,11 +8028,11 @@
         <v>45453</v>
       </c>
       <c r="N3" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O3" s="57"/>
     </row>
-    <row r="4" spans="1:15" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>3</v>
       </c>
@@ -8127,16 +8043,16 @@
         <v>67</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H4" s="27" t="s">
         <v>68</v>
@@ -8145,10 +8061,10 @@
         <v>1</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K4" s="94" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L4" s="31">
         <v>243001650</v>
@@ -8157,13 +8073,13 @@
         <v>45609</v>
       </c>
       <c r="N4" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O4" s="57" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
         <v>4</v>
       </c>
@@ -8171,16 +8087,16 @@
         <v>69</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G5" s="27" t="s">
         <v>70</v>
@@ -8195,7 +8111,7 @@
         <v>72</v>
       </c>
       <c r="K5" s="95" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L5" s="31">
         <v>241010808</v>
@@ -8204,30 +8120,30 @@
         <v>45609</v>
       </c>
       <c r="N5" s="35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O5" s="57" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="32">
         <v>5</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="27" t="s">
         <v>58</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G6" s="27" t="s">
         <v>59</v>
@@ -8251,11 +8167,11 @@
         <v>45453</v>
       </c>
       <c r="N6" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O6" s="57"/>
     </row>
-    <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="32">
         <v>6</v>
       </c>
@@ -8266,19 +8182,19 @@
         <v>73</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I7" s="29">
         <v>1</v>
@@ -8296,28 +8212,28 @@
         <v>75</v>
       </c>
       <c r="N7" s="35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O7" s="57"/>
     </row>
-    <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="32">
         <v>7</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" s="27" t="s">
         <v>76</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G8" s="27" t="s">
         <v>77</v>
@@ -8341,31 +8257,31 @@
         <v>75</v>
       </c>
       <c r="N8" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O8" s="57"/>
     </row>
-    <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="32">
         <v>8</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H9" s="27" t="s">
         <v>81</v>
@@ -8386,40 +8302,40 @@
         <v>45717</v>
       </c>
       <c r="N9" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O9" s="57"/>
     </row>
-    <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="32">
         <v>9</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H10" s="27" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I10" s="30">
         <v>1</v>
       </c>
       <c r="J10" s="35" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K10" s="94">
         <v>45964</v>
@@ -8429,24 +8345,24 @@
       <c r="N10" s="35"/>
       <c r="O10" s="57"/>
     </row>
-    <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="32">
         <v>10</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>83</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G11" s="27" t="s">
         <v>84</v>
@@ -8470,33 +8386,33 @@
         <v>45717</v>
       </c>
       <c r="N11" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O11" s="57" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="32">
         <v>11</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>87</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H12" s="27" t="s">
         <v>88</v>
@@ -8517,28 +8433,28 @@
         <v>45719</v>
       </c>
       <c r="N12" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O12" s="57"/>
     </row>
-    <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="32">
         <v>12</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>90</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G13" s="27" t="s">
         <v>91</v>
@@ -8562,28 +8478,28 @@
         <v>45735</v>
       </c>
       <c r="N13" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O13" s="57"/>
     </row>
-    <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="32">
         <v>13</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G14" s="27" t="s">
         <v>94</v>
@@ -8607,28 +8523,28 @@
         <v>75</v>
       </c>
       <c r="N14" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O14" s="57"/>
     </row>
-    <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="32">
         <v>14</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>54</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G15" s="27" t="s">
         <v>55</v>
@@ -8652,28 +8568,28 @@
         <v>45453</v>
       </c>
       <c r="N15" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O15" s="57"/>
     </row>
-    <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32">
         <v>15</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="27" t="s">
         <v>98</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G16" s="27" t="s">
         <v>99</v>
@@ -8697,28 +8613,28 @@
         <v>45874</v>
       </c>
       <c r="N16" s="35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O16" s="57"/>
     </row>
-    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="32">
         <v>16</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G17" s="27" t="s">
         <v>102</v>
@@ -8742,11 +8658,11 @@
         <v>97</v>
       </c>
       <c r="N17" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O17" s="57"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="57"/>
       <c r="B18" s="57"/>
       <c r="C18" s="57"/>
@@ -8772,15 +8688,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC9CB67-069E-4DDA-927B-C96C93506AB7}">
   <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" style="63" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.77734375" style="63" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" style="63" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.1640625" style="63" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="63" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="63" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" style="63" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="63" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" style="63" customWidth="1"/>
-    <col min="7" max="7" width="25.5" style="63" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.44140625" style="63" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.6640625" style="63" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="4.6640625" style="63" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22" style="63" bestFit="1" customWidth="1"/>
@@ -8792,24 +8708,24 @@
     <col min="16" max="16384" width="9.33203125" style="63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="59" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="59" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="45" t="s">
         <v>134</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="D1" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1" s="68" t="s">
-        <v>151</v>
-      </c>
-      <c r="F1" s="45" t="s">
-        <v>136</v>
       </c>
       <c r="G1" s="45" t="s">
         <v>2</v>
@@ -8818,51 +8734,51 @@
         <v>3</v>
       </c>
       <c r="I1" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="J1" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" s="93" t="s">
         <v>137</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="L1" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="K1" s="93" t="s">
+      <c r="M1" s="93" t="s">
         <v>139</v>
-      </c>
-      <c r="L1" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="M1" s="93" t="s">
-        <v>141</v>
       </c>
       <c r="N1" s="45" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="60">
         <v>1</v>
       </c>
       <c r="B2" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2" s="48" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>109</v>
-      </c>
       <c r="G2" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I2" s="39">
         <v>1</v>
@@ -8880,35 +8796,35 @@
         <v>45405</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O2" s="61"/>
       <c r="P2" s="62"/>
     </row>
-    <row r="3" spans="1:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="64">
         <v>2</v>
       </c>
       <c r="B3" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" s="48" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>109</v>
-      </c>
       <c r="G3" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I3" s="39">
         <v>1</v>
@@ -8931,36 +8847,36 @@
       <c r="O3" s="61"/>
       <c r="P3" s="62"/>
     </row>
-    <row r="4" spans="1:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="64">
         <v>2</v>
       </c>
       <c r="B4" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="F4" s="48" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="F4" s="48" t="s">
-        <v>109</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>156</v>
-      </c>
       <c r="H4" s="26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I4" s="39">
         <v>1</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K4" s="100">
         <v>45752</v>
@@ -8973,36 +8889,36 @@
       <c r="O4" s="61"/>
       <c r="P4" s="62"/>
     </row>
-    <row r="5" spans="1:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="64">
         <v>2</v>
       </c>
       <c r="B5" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="F5" s="48" t="s">
         <v>108</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="D5" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="F5" s="48" t="s">
-        <v>109</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>157</v>
-      </c>
       <c r="H5" s="26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I5" s="39">
         <v>1</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K5" s="100">
         <v>45295</v>
@@ -9019,7 +8935,7 @@
       <c r="O5" s="61"/>
       <c r="P5" s="62"/>
     </row>
-    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="49">
         <v>3</v>
       </c>
@@ -9027,19 +8943,19 @@
         <v>40</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F6" s="48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>41</v>
@@ -9060,12 +8976,12 @@
         <v>45921</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O6" s="61"/>
       <c r="P6" s="62"/>
     </row>
-    <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="50">
         <v>4</v>
       </c>
@@ -9076,13 +8992,13 @@
         <v>47</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F7" s="48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G7" s="12">
         <v>2920.0019080000002</v>
@@ -9106,35 +9022,35 @@
         <v>50</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O7" s="65"/>
       <c r="P7" s="66"/>
     </row>
-    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="52">
         <v>5</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>44</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I8" s="41">
         <v>1</v>
@@ -9152,12 +9068,12 @@
         <v>45404</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O8" s="65"/>
       <c r="P8" s="66"/>
     </row>
-    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="32"/>
       <c r="B9" s="27"/>
       <c r="C9" s="27"/>
@@ -9174,7 +9090,7 @@
       <c r="N9" s="35"/>
       <c r="O9" s="57"/>
     </row>
-    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="30"/>
       <c r="B10" s="28"/>
       <c r="C10" s="27"/>
@@ -9191,7 +9107,7 @@
       <c r="N10" s="35"/>
       <c r="O10" s="57"/>
     </row>
-    <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="29"/>
       <c r="B11" s="28"/>
       <c r="C11" s="27"/>
@@ -9208,7 +9124,7 @@
       <c r="N11" s="35"/>
       <c r="O11" s="57"/>
     </row>
-    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="30"/>
       <c r="B12" s="28"/>
       <c r="C12" s="27"/>
@@ -9225,7 +9141,7 @@
       <c r="N12" s="35"/>
       <c r="O12" s="57"/>
     </row>
-    <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="30"/>
       <c r="B13" s="27"/>
       <c r="C13" s="27"/>
@@ -9242,7 +9158,7 @@
       <c r="N13" s="35"/>
       <c r="O13" s="57"/>
     </row>
-    <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
       <c r="C14" s="33"/>
@@ -9259,7 +9175,7 @@
       <c r="N14" s="35"/>
       <c r="O14" s="57"/>
     </row>
-    <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="29"/>
       <c r="B15" s="27"/>
       <c r="C15" s="28"/>
@@ -9276,7 +9192,7 @@
       <c r="N15" s="35"/>
       <c r="O15" s="57"/>
     </row>
-    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32"/>
       <c r="B16" s="28"/>
       <c r="C16" s="27"/>
@@ -9293,7 +9209,7 @@
       <c r="N16" s="35"/>
       <c r="O16" s="57"/>
     </row>
-    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="29"/>
       <c r="B17" s="27"/>
       <c r="C17" s="27"/>
@@ -9310,7 +9226,7 @@
       <c r="N17" s="35"/>
       <c r="O17" s="57"/>
     </row>
-    <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="30"/>
       <c r="B18" s="28"/>
       <c r="C18" s="27"/>
@@ -9327,7 +9243,7 @@
       <c r="N18" s="35"/>
       <c r="O18" s="57"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="57"/>
       <c r="B19" s="57"/>
       <c r="C19" s="57"/>

--- a/data/FRS_cleaned/Dec/Fmn D Dec/WorkOrderRemote_Dec 2025 D.xlsx
+++ b/data/FRS_cleaned/Dec/Fmn D Dec/WorkOrderRemote_Dec 2025 D.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anu\APT\apt\army\fortwilliam\code\fwDemo\data\FRS_cleaned\Dec\Fmn D Dec\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B176F10-2386-41E4-8C59-E63184700CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C3EAA1-79CC-41C9-A26A-50D841ACD4D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="-14745" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Eng" sheetId="2" r:id="rId1"/>
     <sheet name="EOA Spares" sheetId="3" r:id="rId2"/>
-    <sheet name="MUA" sheetId="4" r:id="rId3"/>
+    <sheet name="VOR Spares" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="180">
   <si>
     <r>
       <rPr>
@@ -634,37 +634,6 @@
         <family val="2"/>
       </rPr>
       <t>26</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>NVR</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363634"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>VR</t>
     </r>
   </si>
   <si>
@@ -6620,7 +6589,27 @@
     <t>Category</t>
   </si>
   <si>
-    <t>Unit</t>
+    <t>NYR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363634"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>R</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -6935,9 +6924,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7224,6 +7210,9 @@
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7539,77 +7528,77 @@
     <col min="7" max="7" width="25.33203125" customWidth="1"/>
     <col min="8" max="8" width="50.44140625" customWidth="1"/>
     <col min="10" max="10" width="22.77734375" customWidth="1"/>
-    <col min="11" max="11" width="14.109375" style="88" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" style="87" customWidth="1"/>
     <col min="12" max="12" width="14.77734375" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" style="88" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" style="87" customWidth="1"/>
     <col min="15" max="15" width="46.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="E1" s="67" t="s">
-        <v>149</v>
-      </c>
-      <c r="F1" s="17" t="s">
+      <c r="B1" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="66" t="s">
+        <v>147</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="21" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="84" t="s">
+      <c r="K1" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="L1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="84" t="s">
-        <v>114</v>
-      </c>
-      <c r="N1" s="22" t="s">
+      <c r="M1" s="83" t="s">
+        <v>112</v>
+      </c>
+      <c r="N1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="14" t="s">
-        <v>106</v>
+      <c r="O1" s="13" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+      <c r="A2" s="14">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="21" t="s">
+      <c r="B2" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>108</v>
+      <c r="D2" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>106</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -7617,252 +7606,252 @@
       <c r="H2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="9">
         <v>1</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="85">
+      <c r="K2" s="84">
         <v>45578</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="100" t="s">
+        <v>178</v>
+      </c>
+      <c r="M2" s="88" t="s">
+        <v>179</v>
+      </c>
+      <c r="N2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="89" t="s">
+      <c r="O2" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+      <c r="A3" s="14">
         <v>2</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="H3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="I3" s="10">
+        <v>1</v>
+      </c>
+      <c r="J3" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="K3" s="84">
+        <v>45943</v>
+      </c>
+      <c r="L3" s="6">
+        <v>251017983</v>
+      </c>
+      <c r="M3" s="89">
+        <v>45988</v>
+      </c>
+      <c r="N3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="11">
-        <v>1</v>
-      </c>
-      <c r="J3" s="19" t="s">
+      <c r="O3" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="K3" s="85">
-        <v>45943</v>
-      </c>
-      <c r="L3" s="7">
-        <v>251017983</v>
-      </c>
-      <c r="M3" s="90">
-        <v>45988</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
+      <c r="A4" s="14">
         <v>3</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="H4" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="G4" s="69" t="s">
+      <c r="I4" s="69">
+        <v>1</v>
+      </c>
+      <c r="J4" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="69" t="s">
+      <c r="K4" s="84">
+        <v>45959</v>
+      </c>
+      <c r="L4" s="70">
+        <v>251018435</v>
+      </c>
+      <c r="M4" s="90">
+        <v>45988</v>
+      </c>
+      <c r="N4" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="O4" s="72" t="s">
         <v>28</v>
-      </c>
-      <c r="I4" s="70">
-        <v>1</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="85">
-        <v>45959</v>
-      </c>
-      <c r="L4" s="71">
-        <v>251018435</v>
-      </c>
-      <c r="M4" s="91">
-        <v>45988</v>
-      </c>
-      <c r="N4" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" s="73" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="74">
+      <c r="A5" s="73">
         <v>4</v>
       </c>
-      <c r="B5" s="75" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="76" t="s">
+      <c r="B5" s="74" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="75" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="76" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="76" t="s">
+        <v>159</v>
+      </c>
+      <c r="F5" s="77" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="77" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="77" t="s">
-        <v>161</v>
-      </c>
-      <c r="F5" s="78" t="s">
-        <v>108</v>
-      </c>
-      <c r="G5" s="27" t="s">
+      <c r="I5" s="78">
+        <v>1</v>
+      </c>
+      <c r="J5" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="K5" s="85">
+        <v>45961</v>
+      </c>
+      <c r="L5" s="79">
+        <v>251017997</v>
+      </c>
+      <c r="M5" s="91">
+        <v>45988</v>
+      </c>
+      <c r="N5" s="80" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="79">
+    </row>
+    <row r="6" spans="1:15" s="62" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="73">
+        <v>5</v>
+      </c>
+      <c r="B6" s="82" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="75" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" s="82" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" s="82" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="82">
         <v>1</v>
       </c>
-      <c r="J5" s="76" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" s="86">
-        <v>45961</v>
-      </c>
-      <c r="L5" s="80">
-        <v>251017997</v>
-      </c>
-      <c r="M5" s="92">
-        <v>45988</v>
-      </c>
-      <c r="N5" s="81" t="s">
-        <v>22</v>
-      </c>
-      <c r="O5" s="82" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" s="63" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="74">
-        <v>5</v>
-      </c>
-      <c r="B6" s="83" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="76" t="s">
+      <c r="J6" s="75" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="83" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" s="83" t="s">
-        <v>150</v>
-      </c>
-      <c r="F6" s="83" t="s">
-        <v>108</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="H6" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="83">
-        <v>1</v>
-      </c>
-      <c r="J6" s="76" t="s">
-        <v>169</v>
-      </c>
-      <c r="K6" s="87">
+      <c r="K6" s="86">
         <v>45963</v>
       </c>
-      <c r="L6" s="83"/>
-      <c r="M6" s="87"/>
-      <c r="N6" s="83"/>
-      <c r="O6" s="83"/>
+      <c r="L6" s="82"/>
+      <c r="M6" s="86"/>
+      <c r="N6" s="82"/>
+      <c r="O6" s="82"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="74">
+      <c r="A7" s="73">
         <v>6</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="82" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" s="75" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" s="82" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" s="82" t="s">
+        <v>148</v>
+      </c>
+      <c r="F7" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="G7" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="C7" s="76" t="s">
+      <c r="H7" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="82">
+        <v>1</v>
+      </c>
+      <c r="J7" s="75" t="s">
         <v>176</v>
       </c>
-      <c r="D7" s="83" t="s">
-        <v>127</v>
-      </c>
-      <c r="E7" s="83" t="s">
-        <v>150</v>
-      </c>
-      <c r="F7" s="83" t="s">
-        <v>108</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="H7" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="83">
-        <v>1</v>
-      </c>
-      <c r="J7" s="76" t="s">
-        <v>178</v>
-      </c>
-      <c r="K7" s="87">
+      <c r="K7" s="86">
         <v>45986</v>
       </c>
-      <c r="L7" s="83">
+      <c r="L7" s="82">
         <v>7643097</v>
       </c>
-      <c r="M7" s="87">
+      <c r="M7" s="86">
         <v>45989</v>
       </c>
-      <c r="N7" s="83" t="s">
-        <v>112</v>
-      </c>
-      <c r="O7" s="83"/>
+      <c r="N7" s="82" t="s">
+        <v>110</v>
+      </c>
+      <c r="O7" s="82"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7875,809 +7864,809 @@
   <dimension ref="A1:O18"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="58"/>
-    <col min="2" max="2" width="14" style="58" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" style="58" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" style="58" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" style="58" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="58" customWidth="1"/>
-    <col min="7" max="7" width="32.6640625" style="58" customWidth="1"/>
-    <col min="8" max="8" width="44.44140625" style="58" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" style="58"/>
-    <col min="10" max="10" width="33.33203125" style="58" customWidth="1"/>
-    <col min="11" max="11" width="14" style="97" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" style="58" customWidth="1"/>
-    <col min="13" max="13" width="14.77734375" style="97" customWidth="1"/>
-    <col min="14" max="14" width="9.33203125" style="58"/>
-    <col min="15" max="15" width="60.109375" style="58" customWidth="1"/>
-    <col min="16" max="16384" width="9.33203125" style="58"/>
+    <col min="1" max="1" width="9.33203125" style="57"/>
+    <col min="2" max="2" width="14" style="57" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="57" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" style="57" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" style="57" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="57" customWidth="1"/>
+    <col min="7" max="7" width="32.6640625" style="57" customWidth="1"/>
+    <col min="8" max="8" width="44.44140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" style="57"/>
+    <col min="10" max="10" width="33.33203125" style="57" customWidth="1"/>
+    <col min="11" max="11" width="14" style="96" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" style="57" customWidth="1"/>
+    <col min="13" max="13" width="14.77734375" style="96" customWidth="1"/>
+    <col min="14" max="14" width="9.33203125" style="57"/>
+    <col min="15" max="15" width="60.109375" style="57" customWidth="1"/>
+    <col min="16" max="16384" width="9.33203125" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="56" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:15" s="55" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="67" t="s">
+        <v>147</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="G1" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="D1" s="44" t="s">
-        <v>128</v>
-      </c>
-      <c r="E1" s="68" t="s">
-        <v>180</v>
-      </c>
-      <c r="F1" s="45" t="s">
+      <c r="J1" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="G1" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="46" t="s">
+      <c r="K1" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="L1" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="K1" s="93" t="s">
+      <c r="M1" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="L1" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="M1" s="93" t="s">
-        <v>139</v>
-      </c>
-      <c r="N1" s="45" t="s">
+      <c r="N1" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="54" t="s">
-        <v>106</v>
+      <c r="O1" s="53" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32">
+      <c r="A2" s="31">
         <v>1</v>
       </c>
-      <c r="B2" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="C2" s="27" t="s">
+      <c r="B2" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="31">
+        <v>1</v>
+      </c>
+      <c r="J2" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="F2" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G2" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="I2" s="32">
-        <v>1</v>
-      </c>
-      <c r="J2" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" s="94">
+      <c r="K2" s="93">
         <v>45057</v>
       </c>
-      <c r="L2" s="36">
+      <c r="L2" s="35">
         <v>4503235454</v>
       </c>
-      <c r="M2" s="94">
+      <c r="M2" s="93">
         <v>45814</v>
       </c>
-      <c r="N2" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="O2" s="57" t="s">
-        <v>148</v>
+      <c r="N2" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="O2" s="56" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="32">
+      <c r="A3" s="31">
         <v>2</v>
       </c>
-      <c r="B3" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="27" t="s">
+      <c r="B3" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="F3" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" s="27" t="s">
+      <c r="I3" s="29">
+        <v>1</v>
+      </c>
+      <c r="J3" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="30">
-        <v>1</v>
-      </c>
-      <c r="J3" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="K3" s="94">
+      <c r="K3" s="93">
         <v>45432</v>
       </c>
-      <c r="L3" s="36">
+      <c r="L3" s="35">
         <v>241001945</v>
       </c>
-      <c r="M3" s="94">
+      <c r="M3" s="93">
         <v>45453</v>
       </c>
-      <c r="N3" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="O3" s="57"/>
+      <c r="N3" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="O3" s="56"/>
     </row>
     <row r="4" spans="1:15" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32">
+      <c r="A4" s="31">
         <v>3</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="H4" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="I4" s="30">
+      <c r="I4" s="29">
         <v>1</v>
       </c>
-      <c r="J4" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="K4" s="94" t="s">
-        <v>125</v>
-      </c>
-      <c r="L4" s="31">
+      <c r="J4" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="K4" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="L4" s="30">
         <v>243001650</v>
       </c>
-      <c r="M4" s="94">
+      <c r="M4" s="93">
         <v>45609</v>
       </c>
-      <c r="N4" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="O4" s="57" t="s">
-        <v>113</v>
+      <c r="N4" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="O4" s="56" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32">
+      <c r="A5" s="31">
         <v>4</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="I5" s="29">
+        <v>1</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" s="94" t="s">
+        <v>124</v>
+      </c>
+      <c r="L5" s="30">
+        <v>241010808</v>
+      </c>
+      <c r="M5" s="93">
+        <v>45609</v>
+      </c>
+      <c r="N5" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="O5" s="56" t="s">
         <v>146</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G5" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="I5" s="30">
-        <v>1</v>
-      </c>
-      <c r="J5" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" s="95" t="s">
-        <v>126</v>
-      </c>
-      <c r="L5" s="31">
-        <v>241010808</v>
-      </c>
-      <c r="M5" s="94">
-        <v>45609</v>
-      </c>
-      <c r="N5" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="O5" s="57" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32">
+      <c r="A6" s="31">
         <v>5</v>
       </c>
-      <c r="B6" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="27" t="s">
+      <c r="B6" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G6" s="27" t="s">
+      <c r="I6" s="28">
+        <v>1</v>
+      </c>
+      <c r="J6" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="29">
-        <v>1</v>
-      </c>
-      <c r="J6" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="K6" s="94">
+      <c r="K6" s="93">
         <v>45432</v>
       </c>
-      <c r="L6" s="36">
+      <c r="L6" s="35">
         <v>241001944</v>
       </c>
-      <c r="M6" s="94">
+      <c r="M6" s="93">
         <v>45453</v>
       </c>
-      <c r="N6" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="O6" s="57"/>
+      <c r="N6" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="O6" s="56"/>
     </row>
     <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32">
+      <c r="A7" s="31">
         <v>6</v>
       </c>
-      <c r="B7" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="27" t="s">
+      <c r="B7" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="H7" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="I7" s="28">
+        <v>1</v>
+      </c>
+      <c r="J7" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="K7" s="93">
+        <v>45696</v>
+      </c>
+      <c r="L7" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="H7" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="I7" s="29">
-        <v>1</v>
-      </c>
-      <c r="J7" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="K7" s="94">
-        <v>45696</v>
-      </c>
-      <c r="L7" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="M7" s="94" t="s">
-        <v>75</v>
-      </c>
-      <c r="N7" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="O7" s="57"/>
+      <c r="M7" s="93" t="s">
+        <v>73</v>
+      </c>
+      <c r="N7" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="O7" s="56"/>
     </row>
     <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32">
+      <c r="A8" s="31">
         <v>7</v>
       </c>
-      <c r="B8" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="27" t="s">
+      <c r="B8" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G8" s="27" t="s">
+      <c r="I8" s="29">
+        <v>1</v>
+      </c>
+      <c r="J8" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="K8" s="93">
+        <v>45981</v>
+      </c>
+      <c r="L8" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="30">
-        <v>1</v>
-      </c>
-      <c r="J8" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="K8" s="94">
-        <v>45981</v>
-      </c>
-      <c r="L8" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="M8" s="94" t="s">
-        <v>75</v>
-      </c>
-      <c r="N8" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="O8" s="57"/>
+      <c r="M8" s="93" t="s">
+        <v>73</v>
+      </c>
+      <c r="N8" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="O8" s="56"/>
     </row>
     <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32">
+      <c r="A9" s="31">
         <v>8</v>
       </c>
-      <c r="B9" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="H9" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="I9" s="30">
+      <c r="B9" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="29">
         <v>1</v>
       </c>
-      <c r="J9" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="K9" s="94">
+      <c r="J9" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="93">
         <v>45702</v>
       </c>
-      <c r="L9" s="36">
+      <c r="L9" s="35">
         <v>241015397</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="93">
         <v>45717</v>
       </c>
-      <c r="N9" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="O9" s="57"/>
+      <c r="N9" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="O9" s="56"/>
     </row>
     <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="A10" s="31">
         <v>9</v>
       </c>
-      <c r="B10" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="F10" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G10" s="27" t="s">
+      <c r="B10" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="H10" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="I10" s="29">
+        <v>1</v>
+      </c>
+      <c r="J10" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="H10" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="I10" s="30">
-        <v>1</v>
-      </c>
-      <c r="J10" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="K10" s="94">
+      <c r="K10" s="93">
         <v>45964</v>
       </c>
-      <c r="L10" s="36"/>
-      <c r="M10" s="94"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="57"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="93"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="56"/>
     </row>
     <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32">
+      <c r="A11" s="31">
         <v>10</v>
       </c>
-      <c r="B11" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11" s="27" t="s">
+      <c r="B11" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="D11" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G11" s="27" t="s">
+      <c r="I11" s="29">
+        <v>1</v>
+      </c>
+      <c r="J11" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H11" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="I11" s="30">
-        <v>1</v>
-      </c>
-      <c r="J11" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="K11" s="94">
+      <c r="K11" s="93">
         <v>45702</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="35">
         <v>241015396</v>
       </c>
-      <c r="M11" s="94">
+      <c r="M11" s="93">
         <v>45717</v>
       </c>
-      <c r="N11" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="O11" s="57" t="s">
-        <v>148</v>
+      <c r="N11" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="O11" s="56" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="32">
+      <c r="A12" s="31">
         <v>11</v>
       </c>
-      <c r="B12" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="27" t="s">
+      <c r="B12" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="H12" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" s="29">
+        <v>1</v>
+      </c>
+      <c r="J12" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="D12" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="F12" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="H12" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="I12" s="30">
-        <v>1</v>
-      </c>
-      <c r="J12" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="K12" s="94">
+      <c r="K12" s="93">
         <v>45709</v>
       </c>
-      <c r="L12" s="36">
+      <c r="L12" s="35">
         <v>241015532</v>
       </c>
-      <c r="M12" s="94">
+      <c r="M12" s="93">
         <v>45719</v>
       </c>
-      <c r="N12" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="O12" s="57"/>
+      <c r="N12" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="O12" s="56"/>
     </row>
     <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32">
+      <c r="A13" s="31">
         <v>12</v>
       </c>
-      <c r="B13" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="27" t="s">
+      <c r="B13" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E13" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G13" s="27" t="s">
+      <c r="I13" s="31">
+        <v>1</v>
+      </c>
+      <c r="J13" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="I13" s="32">
-        <v>1</v>
-      </c>
-      <c r="J13" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="K13" s="94">
+      <c r="K13" s="93">
         <v>45720</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="35">
         <v>241016229</v>
       </c>
-      <c r="M13" s="94">
+      <c r="M13" s="93">
         <v>45735</v>
       </c>
-      <c r="N13" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="O13" s="57"/>
+      <c r="N13" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="O13" s="56"/>
     </row>
     <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="32">
+      <c r="A14" s="31">
         <v>13</v>
       </c>
-      <c r="B14" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E14" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="F14" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G14" s="27" t="s">
+      <c r="B14" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="F14" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="I14" s="29">
+        <v>1</v>
+      </c>
+      <c r="J14" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="H14" s="27" t="s">
+      <c r="K14" s="93">
+        <v>45825</v>
+      </c>
+      <c r="L14" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="I14" s="30">
-        <v>1</v>
-      </c>
-      <c r="J14" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="K14" s="94">
-        <v>45825</v>
-      </c>
-      <c r="L14" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="M14" s="94" t="s">
-        <v>75</v>
-      </c>
-      <c r="N14" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="O14" s="57"/>
+      <c r="M14" s="93" t="s">
+        <v>73</v>
+      </c>
+      <c r="N14" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="O14" s="56"/>
     </row>
     <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="32">
+      <c r="A15" s="31">
         <v>14</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C15" s="27" t="s">
+      <c r="B15" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="F15" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G15" s="27" t="s">
+      <c r="I15" s="29">
+        <v>1</v>
+      </c>
+      <c r="J15" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H15" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="I15" s="30">
-        <v>1</v>
-      </c>
-      <c r="J15" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="K15" s="94">
+      <c r="K15" s="93">
         <v>45432</v>
       </c>
-      <c r="L15" s="31">
+      <c r="L15" s="30">
         <v>241001943</v>
       </c>
-      <c r="M15" s="94">
+      <c r="M15" s="93">
         <v>45453</v>
       </c>
-      <c r="N15" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="O15" s="57"/>
+      <c r="N15" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="O15" s="56"/>
     </row>
     <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="32">
+      <c r="A16" s="31">
         <v>15</v>
       </c>
-      <c r="B16" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="C16" s="27" t="s">
+      <c r="B16" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="H16" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="F16" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G16" s="27" t="s">
+      <c r="I16" s="28">
+        <v>1</v>
+      </c>
+      <c r="J16" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="H16" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="I16" s="29">
-        <v>1</v>
-      </c>
-      <c r="J16" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="K16" s="94">
+      <c r="K16" s="93">
         <v>45675</v>
       </c>
-      <c r="L16" s="36">
+      <c r="L16" s="35">
         <v>251009621</v>
       </c>
-      <c r="M16" s="94">
+      <c r="M16" s="93">
         <v>45874</v>
       </c>
-      <c r="N16" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="O16" s="57"/>
+      <c r="N16" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="O16" s="56"/>
     </row>
     <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="32">
+      <c r="A17" s="31">
         <v>16</v>
       </c>
-      <c r="B17" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" s="27" t="s">
+      <c r="B17" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="F17" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G17" s="27" t="s">
+      <c r="D17" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="28">
+        <v>1</v>
+      </c>
+      <c r="J17" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H17" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="I17" s="29">
-        <v>1</v>
-      </c>
-      <c r="J17" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="K17" s="94">
+      <c r="K17" s="93">
         <v>45897</v>
       </c>
-      <c r="L17" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="M17" s="94" t="s">
-        <v>97</v>
-      </c>
-      <c r="N17" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="O17" s="57"/>
+      <c r="L17" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="M17" s="93" t="s">
+        <v>95</v>
+      </c>
+      <c r="N17" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="O17" s="56"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="57"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="96"/>
-      <c r="L18" s="57"/>
-      <c r="M18" s="96"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="57"/>
+      <c r="A18" s="56"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="95"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="95"/>
+      <c r="N18" s="56"/>
+      <c r="O18" s="56"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
@@ -8690,575 +8679,575 @@
   <dimension ref="A1:P19"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.77734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="63" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" style="63" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="63" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="63" customWidth="1"/>
-    <col min="7" max="7" width="25.44140625" style="63" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.6640625" style="63" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.6640625" style="63" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22" style="63" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" style="99" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" style="63" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" style="99" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.33203125" style="63" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.33203125" style="63" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.33203125" style="63"/>
+    <col min="1" max="1" width="6.77734375" style="62" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="62" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="62" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="62" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="62" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="62" customWidth="1"/>
+    <col min="7" max="7" width="25.44140625" style="62" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.6640625" style="62" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.6640625" style="62" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22" style="62" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" style="98" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" style="62" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" style="98" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.33203125" style="62" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" style="62" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.33203125" style="62"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="59" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:16" s="58" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="67" t="s">
+        <v>147</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="G1" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="D1" s="44" t="s">
-        <v>128</v>
-      </c>
-      <c r="E1" s="68" t="s">
-        <v>149</v>
-      </c>
-      <c r="F1" s="45" t="s">
+      <c r="J1" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="G1" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="46" t="s">
+      <c r="K1" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="L1" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="K1" s="93" t="s">
+      <c r="M1" s="92" t="s">
         <v>137</v>
       </c>
-      <c r="L1" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="M1" s="93" t="s">
-        <v>139</v>
-      </c>
-      <c r="N1" s="45" t="s">
+      <c r="N1" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="14" t="s">
-        <v>106</v>
+      <c r="O1" s="13" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="60">
+      <c r="A2" s="59">
         <v>1</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="H2" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="I2" s="39">
+      <c r="I2" s="38">
         <v>1</v>
       </c>
-      <c r="J2" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="100">
+      <c r="J2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="99">
         <v>44629</v>
       </c>
-      <c r="L2" s="40">
+      <c r="L2" s="39">
         <v>241000273</v>
       </c>
-      <c r="M2" s="98">
+      <c r="M2" s="97">
         <v>45405</v>
       </c>
-      <c r="N2" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="62"/>
+      <c r="N2" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="O2" s="60"/>
+      <c r="P2" s="61"/>
     </row>
     <row r="3" spans="1:16" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64">
+      <c r="A3" s="63">
         <v>2</v>
       </c>
-      <c r="B3" s="47" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H3" s="26" t="s">
+      <c r="B3" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="F3" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="I3" s="39">
+      <c r="H3" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="I3" s="38">
         <v>1</v>
       </c>
-      <c r="J3" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" s="100">
+      <c r="J3" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="99">
         <v>45386</v>
       </c>
-      <c r="L3" s="40">
+      <c r="L3" s="39">
         <v>243000275</v>
       </c>
-      <c r="M3" s="98">
+      <c r="M3" s="97">
         <v>45404</v>
       </c>
-      <c r="N3" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="61"/>
-      <c r="P3" s="62"/>
+      <c r="N3" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="60"/>
+      <c r="P3" s="61"/>
     </row>
     <row r="4" spans="1:16" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="64">
+      <c r="A4" s="63">
         <v>2</v>
       </c>
-      <c r="B4" s="47" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="D4" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="F4" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="I4" s="38">
+        <v>1</v>
+      </c>
+      <c r="J4" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="H4" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="I4" s="39">
-        <v>1</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="K4" s="100">
+      <c r="K4" s="99">
         <v>45752</v>
       </c>
-      <c r="L4" s="40"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" s="61"/>
-      <c r="P4" s="62"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O4" s="60"/>
+      <c r="P4" s="61"/>
     </row>
     <row r="5" spans="1:16" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="64">
+      <c r="A5" s="63">
         <v>2</v>
       </c>
-      <c r="B5" s="47" t="s">
-        <v>107</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="B5" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D5" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="F5" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="I5" s="38">
+        <v>1</v>
+      </c>
+      <c r="J5" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="H5" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="I5" s="39">
-        <v>1</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="K5" s="100">
+      <c r="K5" s="99">
         <v>45295</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="39">
         <v>243000645</v>
       </c>
-      <c r="M5" s="98">
+      <c r="M5" s="97">
         <v>45344</v>
       </c>
-      <c r="N5" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="O5" s="61"/>
-      <c r="P5" s="62"/>
+      <c r="N5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" s="60"/>
+      <c r="P5" s="61"/>
     </row>
     <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="49">
+      <c r="A6" s="48">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="40">
+        <v>1</v>
+      </c>
+      <c r="J6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" s="41">
-        <v>1</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" s="100">
+      <c r="K6" s="99">
         <v>45208</v>
       </c>
-      <c r="L6" s="40">
+      <c r="L6" s="39">
         <v>231011060</v>
       </c>
-      <c r="M6" s="98">
+      <c r="M6" s="97">
         <v>45921</v>
       </c>
-      <c r="N6" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="O6" s="61"/>
-      <c r="P6" s="62"/>
+      <c r="N6" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="O6" s="60"/>
+      <c r="P6" s="61"/>
     </row>
     <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50">
+      <c r="A7" s="49">
         <v>4</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="G7" s="11">
+        <v>2920.0019080000002</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="I7" s="50">
+        <v>1</v>
+      </c>
+      <c r="J7" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="F7" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="G7" s="12">
-        <v>2920.0019080000002</v>
-      </c>
-      <c r="H7" s="9" t="s">
+      <c r="K7" s="99">
+        <v>45388</v>
+      </c>
+      <c r="L7" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="51">
-        <v>1</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="K7" s="100">
-        <v>45388</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="M7" s="98" t="s">
-        <v>50</v>
-      </c>
-      <c r="N7" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="O7" s="65"/>
-      <c r="P7" s="66"/>
+      <c r="M7" s="97" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="O7" s="64"/>
+      <c r="P7" s="65"/>
     </row>
     <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="52">
+      <c r="A8" s="51">
         <v>5</v>
       </c>
-      <c r="B8" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="I8" s="40">
+        <v>1</v>
+      </c>
+      <c r="J8" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="I8" s="41">
-        <v>1</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="K8" s="100">
+      <c r="K8" s="99">
         <v>45386</v>
       </c>
-      <c r="L8" s="53">
+      <c r="L8" s="52">
         <v>241000273</v>
       </c>
-      <c r="M8" s="98">
+      <c r="M8" s="97">
         <v>45404</v>
       </c>
-      <c r="N8" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="O8" s="65"/>
-      <c r="P8" s="66"/>
+      <c r="N8" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="O8" s="64"/>
+      <c r="P8" s="65"/>
     </row>
     <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="94"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="94"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="57"/>
+      <c r="A9" s="31"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="93"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="93"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="56"/>
     </row>
     <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="94"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="94"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="57"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="93"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="93"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="56"/>
     </row>
     <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="94"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="94"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="57"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="93"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="93"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="56"/>
     </row>
     <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="94"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="94"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="57"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="93"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="93"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="56"/>
     </row>
     <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="94"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="94"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="57"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="93"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="93"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="56"/>
     </row>
     <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="94"/>
-      <c r="L14" s="36"/>
-      <c r="M14" s="94"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="57"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="93"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="93"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="56"/>
     </row>
     <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="94"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="94"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="57"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="93"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="93"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="56"/>
     </row>
     <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="32"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="94"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="94"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="57"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="93"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="93"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="56"/>
     </row>
     <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="29"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="94"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="94"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="57"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="93"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="93"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="56"/>
     </row>
     <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="30"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="94"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="94"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="57"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="93"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="93"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="56"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="57"/>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="96"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="96"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
+      <c r="A19" s="56"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="56"/>
+      <c r="K19" s="95"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="95"/>
+      <c r="N19" s="56"/>
+      <c r="O19" s="56"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
